--- a/backend/results.xlsx
+++ b/backend/results.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -598,6 +598,238 @@
         <v>46162.54466435185</v>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>supriya</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>DBT</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>4</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="1" t="n">
+        <v>46165.46386574074</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>amit</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>DBT</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>3</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="1" t="n">
+        <v>46165.4650925926</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>supriya</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>WPT</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>4</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="1" t="n">
+        <v>46165.4655787037</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>rajesh</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>DBT</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>4</v>
+      </c>
+      <c r="E10" t="n">
+        <v>4</v>
+      </c>
+      <c r="F10" t="n">
+        <v>4</v>
+      </c>
+      <c r="G10" s="1" t="n">
+        <v>46165.50149305556</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>supriya</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>4</v>
+      </c>
+      <c r="E11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" s="1" t="n">
+        <v>46167.41486111111</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>supriya</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="1" t="n">
+        <v>46167.48082175926</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>supriya</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>C++</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" s="1" t="n">
+        <v>46167.48233796296</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>amit</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>4</v>
+      </c>
+      <c r="E14" t="n">
+        <v>4</v>
+      </c>
+      <c r="F14" t="n">
+        <v>4</v>
+      </c>
+      <c r="G14" s="1" t="n">
+        <v>46170.52546296296</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
